--- a/samples/ExcelScry-sample.xlsx
+++ b/samples/ExcelScry-sample.xlsx
@@ -20,8 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="hh:mm"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -60,12 +64,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C6:K16"/>
+  <dimension ref="C6:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="3" max="3"/>
@@ -441,6 +448,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="6">
@@ -484,6 +493,11 @@
           <t>Start time</t>
         </is>
       </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
@@ -496,16 +510,16 @@
           <t>Widget</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="4" t="n">
         <v>19.99</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="4" t="n">
         <v>23988</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>46037</v>
       </c>
       <c r="I7" t="inlineStr">
@@ -513,8 +527,11 @@
           <t>repeat customer</t>
         </is>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="6" t="n">
         <v>0.3958333333333333</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="8">
@@ -528,20 +545,23 @@
           <t>Widget</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="4" t="n">
         <v>19.99</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="4" t="n">
         <v>18790.6</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>46056</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="6" t="n">
         <v>0.5453125</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="9">
@@ -555,16 +575,16 @@
           <t>Gadget</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="4" t="n">
         <v>249.5</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>46073</v>
       </c>
       <c r="I9" t="inlineStr">
@@ -572,8 +592,11 @@
           <t>backordered</t>
         </is>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="K9" s="6" t="n">
         <v>0.999988425925926</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -587,22 +610,25 @@
           <t>Gadget</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="4" t="n">
         <v>249.5</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="4" t="n">
         <v>9231.5</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>expedited</t>
         </is>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="11">
@@ -616,16 +642,16 @@
           <t>Doohickey</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3" t="n">
         <v>1.844674407370955e+16</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="4" t="n">
         <v>9223372036854776</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="5" t="n">
         <v>46095</v>
       </c>
       <c r="I11" t="inlineStr">
@@ -633,8 +659,19 @@
           <t>large id</t>
         </is>
       </c>
-    </row>
-    <row r="12"/>
+      <c r="L11" s="7" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="L12" s="7" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
@@ -646,22 +683,25 @@
           <t>Doohickey</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="5" t="n">
         <v>46114</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>rounding</t>
         </is>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
@@ -675,17 +715,20 @@
           <t>Widget</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="4" t="n">
         <v>19.99</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="4" t="n">
         <v>239.88</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="5" t="n">
         <v>46131</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -699,16 +742,16 @@
           <t>Gadget</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="4" t="n">
         <v>249.5</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="4" t="n">
         <v>748.5</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="5" t="n">
         <v>46149</v>
       </c>
       <c r="I15" t="inlineStr">
@@ -728,16 +771,16 @@
           <t>Widget</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="4" t="n">
         <v>19.99</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="4" t="n">
         <v>99.95</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" s="5" t="n">
         <v>46172</v>
       </c>
       <c r="I16" t="inlineStr">
